--- a/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35057E65-9732-4FE6-9F6A-834E020B0B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B61C9590-04F1-4F5F-918F-BD9A3927B3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1290,7 +1290,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E145A39C-C6A4-409F-8C2B-D06A0845C6B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27873E95-8AA2-49EC-9DCF-007B698A8BE7}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1347,7 +1347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FE86E8B-6ACC-4263-AC4D-AAC843AFD38B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21982DE-02BD-4CF3-BAA8-63D055640203}">
   <dimension ref="B9:O34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2141,7 +2141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DDDB19-C621-404C-8AF1-6D478355A4B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F6B0BFC-89A4-41E3-A015-F2FA53D7B8D7}">
   <dimension ref="B9:T67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3927,7 +3927,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{186D16D7-E933-4D8C-B6DF-DBE6CDD0365B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD88488-6C17-4B42-9C7A-A4B88445A232}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3F709A-5770-42FE-9703-D104D553F18E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75B5993-64CD-4213-BF88-DB85C198C1C1}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4020,7 +4020,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB8709D9-F3BA-47FD-941B-129A96ECD08A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7052BB89-E16B-4582-8700-42ED30F90690}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4058,7 +4058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A24064-00E3-471D-966C-9C294A000603}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A596C3-90B5-46EA-BDE6-A700EFA9B091}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4090,7 +4090,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.11301666666666667</v>
+        <v>0.11301666666666665</v>
       </c>
       <c r="E11" t="s">
         <v>181</v>
@@ -4132,7 +4132,7 @@
         <v>37</v>
       </c>
       <c r="D14">
-        <v>0.14051666666666668</v>
+        <v>0.14051666666666665</v>
       </c>
       <c r="E14" t="s">
         <v>181</v>
@@ -4160,7 +4160,7 @@
         <v>37</v>
       </c>
       <c r="D16">
-        <v>0.17300833333333332</v>
+        <v>0.17300833333333335</v>
       </c>
       <c r="E16" t="s">
         <v>181</v>
@@ -4230,7 +4230,7 @@
         <v>37</v>
       </c>
       <c r="D21">
-        <v>0.14675000000000002</v>
+        <v>0.14674999999999999</v>
       </c>
       <c r="E21" t="s">
         <v>181</v>
@@ -4272,7 +4272,7 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0.17686666666666664</v>
+        <v>0.1768666666666667</v>
       </c>
       <c r="E24" t="s">
         <v>181</v>
@@ -4286,7 +4286,7 @@
         <v>37</v>
       </c>
       <c r="D25">
-        <v>0.12750833333333336</v>
+        <v>0.12750833333333333</v>
       </c>
       <c r="E25" t="s">
         <v>181</v>
@@ -4300,7 +4300,7 @@
         <v>37</v>
       </c>
       <c r="D26">
-        <v>0.15992500000000001</v>
+        <v>0.15992499999999998</v>
       </c>
       <c r="E26" t="s">
         <v>181</v>
@@ -4314,7 +4314,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.17169166666666666</v>
+        <v>0.17169166666666669</v>
       </c>
       <c r="E27" t="s">
         <v>181</v>
@@ -4370,7 +4370,7 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>0.11987500000000001</v>
+        <v>0.119875</v>
       </c>
       <c r="E31" t="s">
         <v>181</v>
@@ -4384,7 +4384,7 @@
         <v>37</v>
       </c>
       <c r="D32">
-        <v>0.15713333333333335</v>
+        <v>0.15713333333333332</v>
       </c>
       <c r="E32" t="s">
         <v>181</v>
@@ -4398,7 +4398,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.17700833333333332</v>
+        <v>0.17700833333333335</v>
       </c>
       <c r="E33" t="s">
         <v>181</v>
@@ -4440,7 +4440,7 @@
         <v>37</v>
       </c>
       <c r="D36">
-        <v>0.11254166666666665</v>
+        <v>0.11254166666666666</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -4454,7 +4454,7 @@
         <v>37</v>
       </c>
       <c r="D37">
-        <v>0.11206666666666666</v>
+        <v>0.11206666666666665</v>
       </c>
       <c r="E37" t="s">
         <v>181</v>
